--- a/data/usa/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:BC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,200 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -645,7 +715,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
@@ -701,83 +771,111 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>25.81818181818182</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.6375</v>
+        <v>186</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>68.08484848484848</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>3378929.924242424</v>
+        <v>63</v>
       </c>
       <c r="U2" t="n">
-        <v>72.04848484848485</v>
+        <v>50000</v>
       </c>
       <c r="V2" t="n">
-        <v>26.82326388888889</v>
-      </c>
-      <c r="W2" t="n">
-        <v>178.7697916666667</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.177083333333333</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>69.28194444444445</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2437809.027777778</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>72.42395833333333</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>23.98889998889999</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>179.8143384393385</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>25.71515151515151</v>
       </c>
       <c r="AE2" t="n">
-        <v>65.21193736818738</v>
+        <v>181.5777777777778</v>
       </c>
       <c r="AF2" t="n">
-        <v>2111315.663503163</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>71.33468961593961</v>
+        <v>67.96848484848485</v>
       </c>
       <c r="AH2" t="n">
-        <v>24.66446344842285</v>
+        <v>3256979.797979798</v>
       </c>
       <c r="AI2" t="n">
-        <v>177.4474344629156</v>
+        <v>71.9670707070707</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.183539801790281</v>
+        <v>26.74087301587302</v>
       </c>
       <c r="AK2" t="n">
-        <v>66.9036058716965</v>
+        <v>179.3992063492063</v>
       </c>
       <c r="AL2" t="n">
-        <v>2834091.145833333</v>
+        <v>1.173809523809524</v>
       </c>
       <c r="AM2" t="n">
-        <v>73.34018941815856</v>
-      </c>
-      <c r="AN2" t="inlineStr">
+        <v>69.20793650793651</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2479353.174603175</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>72.44166666666668</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>24.10215617715618</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>179.5005869130869</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>65.57434648684651</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2294799.034299034</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>71.5803071928072</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>24.80224394105468</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>177.7802049080502</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.188331202046036</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>66.88983528193886</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2760425.595238095</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>73.11735933503836</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>zoZ995af</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>tOpyQa24</t>
         </is>
@@ -794,7 +892,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
@@ -846,83 +944,125 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.26666666666667</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.1685185185186</v>
+        <v>179</v>
       </c>
       <c r="R3" t="n">
-        <v>1.053703703703704</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>67.10740740740739</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1762638.888888889</v>
+        <v>75</v>
       </c>
       <c r="U3" t="n">
-        <v>71.24444444444445</v>
+        <v>7500000</v>
       </c>
       <c r="V3" t="n">
-        <v>25.06700336700337</v>
+        <v>78</v>
       </c>
       <c r="W3" t="n">
-        <v>182.6554292929293</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>1.212710437710438</v>
+        <v>177</v>
       </c>
       <c r="Y3" t="n">
-        <v>66.53160774410775</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1983490.109427609</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>70.77521043771044</v>
+        <v>129</v>
       </c>
       <c r="AB3" t="n">
-        <v>26.05484749455338</v>
+        <v>1975000</v>
       </c>
       <c r="AC3" t="n">
-        <v>181.1303376906318</v>
+        <v>140</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.074945533769063</v>
+        <v>26.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.87941176470589</v>
+        <v>181.1822222222223</v>
       </c>
       <c r="AF3" t="n">
-        <v>1225298.202614379</v>
+        <v>1.064444444444444</v>
       </c>
       <c r="AG3" t="n">
-        <v>70.50310457516339</v>
+        <v>67.1888888888889</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.62749766573296</v>
+        <v>1839666.666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>181.8678026766262</v>
+        <v>70.89333333333335</v>
       </c>
       <c r="AJ3" t="n">
+        <v>25.17558922558922</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>182.3321548821549</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.191582491582492</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>66.94208754208753</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2060681.818181818</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>70.88249158249158</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>25.79668655868145</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>180.4664052287582</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.073796533105996</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>66.03312020460359</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1435218.456947997</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>71.12160272804775</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>23.80319211017741</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>182.152293417367</v>
+      </c>
+      <c r="AX3" t="n">
         <v>1.019607843137255</v>
       </c>
-      <c r="AK3" t="n">
-        <v>62.32547463429817</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1080415.305010893</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>68.98210395269219</v>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AY3" t="n">
+        <v>62.80070611577964</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1130583.129084967</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>69.09622432306256</v>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>rXawJi8t</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2PIEeC7j</t>
         </is>
@@ -939,7 +1079,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
@@ -991,83 +1131,125 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>22.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="Q4" t="n">
-        <v>180.2</v>
+        <v>185</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>65.73333333333333</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>2086166.666666667</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>73.56666666666666</v>
+        <v>100000</v>
       </c>
       <c r="V4" t="n">
-        <v>27.46233766233766</v>
+        <v>61</v>
       </c>
       <c r="W4" t="n">
-        <v>180.9974025974026</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>1.054545454545454</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="Y4" t="n">
-        <v>65.9064935064935</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1204441.558441559</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>68.75844155844156</v>
+        <v>199</v>
       </c>
       <c r="AB4" t="n">
-        <v>23.27406905744754</v>
+        <v>3075000</v>
       </c>
       <c r="AC4" t="n">
-        <v>181.6231295149639</v>
+        <v>207</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>22.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>63.41337074303406</v>
+        <v>180.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>1260498.803176241</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="n">
-        <v>71.32203087375301</v>
+        <v>65.67999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>26.15272271588061</v>
+        <v>2039000</v>
       </c>
       <c r="AI4" t="n">
-        <v>179.7734954268789</v>
+        <v>73.42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.087012173290369</v>
+        <v>27.49350649350649</v>
       </c>
       <c r="AK4" t="n">
-        <v>64.29777121374866</v>
+        <v>180.7922077922078</v>
       </c>
       <c r="AL4" t="n">
-        <v>1105770.949288806</v>
+        <v>1.051948051948052</v>
       </c>
       <c r="AM4" t="n">
-        <v>68.04186358754029</v>
-      </c>
-      <c r="AN4" t="inlineStr">
+        <v>65.98701298701299</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1200909.090909091</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>68.75324675324676</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>23.35241228070175</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>181.4065789473684</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>63.35486842105263</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1277069.152046784</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>71.19820175438596</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>26.20622356285972</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>179.5871937749512</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.084461152882206</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>64.37136764836994</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1103541.125541126</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>68.03731611637791</v>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>rJ9D8rzj</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>txm4BKVR</t>
         </is>
@@ -1084,7 +1266,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">bazakos f 
   usa </t>
         </is>
       </c>
@@ -1136,83 +1318,125 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>183</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>575000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>64</v>
+      </c>
+      <c r="W5" t="n">
+        <v>21</v>
+      </c>
+      <c r="X5" t="n">
+        <v>185</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>177</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>218</v>
+      </c>
+      <c r="AD5" t="n">
         <v>26.25757575757576</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="AE5" t="n">
         <v>182.8484848484848</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AF5" t="n">
         <v>1.090909090909091</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AG5" t="n">
         <v>68.53030303030303</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AH5" t="n">
         <v>2365151.515151516</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AI5" t="n">
         <v>71.68181818181817</v>
       </c>
-      <c r="V5" t="n">
-        <v>27.06646464646465</v>
-      </c>
-      <c r="W5" t="n">
-        <v>183.3460606060606</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.100404040404041</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>67.13616161616162</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1354939.393939394</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>70.44343434343435</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AJ5" t="n">
+        <v>27.4080808080808</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>183.0575757575758</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.100505050505051</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>67.32020202020202</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1364924.242424242</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>70.27929292929292</v>
+      </c>
+      <c r="AP5" t="n">
         <v>24.87184560132215</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AQ5" t="n">
         <v>180.9194555682685</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AR5" t="n">
         <v>1.006944444444444</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AS5" t="n">
         <v>64.20262840071193</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AT5" t="n">
         <v>1107212.329964404</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AU5" t="n">
         <v>69.16638062547675</v>
       </c>
-      <c r="AH5" t="n">
-        <v>22.70494987468672</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>183.442888471178</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.010526315789474</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>60.95191102756892</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>895474.9373433584</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>69.55391604010025</v>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AV5" t="n">
+        <v>22.98535401002506</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>183.0119439223058</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.013157894736842</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>61.81488878446115</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>995697.8383458648</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>70.15072838345864</v>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>6LuGZiZI</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>nJ01AhXP</t>
         </is>
@@ -1229,7 +1453,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">gonzales g 
   usa </t>
         </is>
       </c>
@@ -1281,83 +1505,125 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>175</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>68</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>68</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>209</v>
+      </c>
+      <c r="AD6" t="n">
         <v>27.23272727272727</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AE6" t="n">
         <v>181.4945454545455</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AF6" t="n">
         <v>1.192727272727273</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AG6" t="n">
         <v>68.55454545454546</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AH6" t="n">
         <v>2028936.363636364</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AI6" t="n">
         <v>71.60727272727273</v>
       </c>
-      <c r="V6" t="n">
-        <v>28.46885521885522</v>
-      </c>
-      <c r="W6" t="n">
-        <v>181.1343434343435</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.401346801346801</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>72.17861952861954</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4009036.195286195</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>74.70404040404041</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AJ6" t="n">
+        <v>28.60303030303031</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>180.7015151515151</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.387878787878788</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>72.35757575757576</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4027651.515151516</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>74.58939393939393</v>
+      </c>
+      <c r="AP6" t="n">
         <v>25.52729315583536</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AQ6" t="n">
         <v>178.0795901370581</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
         <v>65.21619122565414</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AT6" t="n">
         <v>1096387.178394212</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AU6" t="n">
         <v>68.50703106214614</v>
       </c>
-      <c r="AH6" t="n">
-        <v>24.63389780154486</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>179.4720885323826</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.008333333333333</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>67.11437908496733</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1928738.859180036</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>73.82133095662508</v>
-      </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AV6" t="n">
+        <v>25.08525167642815</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>179.6502504031916</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.055952380952381</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>67.4250233426704</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2096077.794754266</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>73.7279602750191</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>UL7r7duf</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>86yPt28f</t>
         </is>
@@ -1374,8 +1640,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">montero r 
-  cos </t>
+          <t xml:space="preserve">chapman a 
+  usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1430,85 +1696,2214 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>25.77818181818181</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="n">
-        <v>176.4581818181818</v>
+        <v>175.5</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>68.9290909090909</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>2707045.454545455</v>
+        <v>131</v>
       </c>
       <c r="U7" t="n">
-        <v>71.7</v>
+        <v>1650000</v>
       </c>
       <c r="V7" t="n">
+        <v>134</v>
+      </c>
+      <c r="W7" t="n">
+        <v>23</v>
+      </c>
+      <c r="X7" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>195</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3650000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>212</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>25.3810606060606</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>176.6742424242424</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>68.99747474747474</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2828598.484848485</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>72.10277777777777</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>25.98181818181818</v>
       </c>
-      <c r="W7" t="n">
-        <v>181.9845598845599</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AK7" t="n">
+        <v>182.153391053391</v>
+      </c>
+      <c r="AL7" t="n">
         <v>1.055844155844156</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AM7" t="n">
         <v>65.45425685425685</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AN7" t="n">
         <v>1634491.341991342</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AO7" t="n">
         <v>69.13477633477632</v>
       </c>
-      <c r="AB7" t="n">
-        <v>25.25575098814229</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>178.3410869565217</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>65.19758234519104</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1288521.739130435</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>69.47237154150199</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AP7" t="n">
+        <v>25.29416996047431</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>178.5049407114624</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>65.23908102766799</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1289512.104743083</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>69.50578063241107</v>
+      </c>
+      <c r="AV7" t="n">
         <v>25.37236188733867</v>
       </c>
-      <c r="AI7" t="n">
-        <v>180.343819082657</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="AW7" t="n">
+        <v>180.4282298804689</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1.035211811997526</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AY7" t="n">
         <v>64.30395636723588</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AZ7" t="n">
         <v>2116914.754298849</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BA7" t="n">
         <v>69.14688461509004</v>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>KtuTuMN0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>lAVQ9RGh</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>167</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>27.12424242424242</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.078787878787879</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>66.9530303030303</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1408492.424242424</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>69.66515151515152</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>27.39848484848485</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>183.430303030303</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.13939393939394</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>68.03030303030305</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3074621.212121212</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>69.62575757575758</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>25.59707602339181</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>179.3770467836257</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>65.30109649122808</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1454587.902046784</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>70.44630847953216</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>27.06470192958953</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>183.2764525337213</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.014492753623188</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>63.34859890561869</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>872897.4709258227</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>65.62857062733561</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>167</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>23.77979797979798</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>179.5129292929293</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.074545454545455</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>66.22161616161615</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1430424.242424242</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>72.22888888888887</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>180.5636363636364</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>68.25454545454545</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2175000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>23.54262360446571</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>178.3436602870813</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.087041467304625</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>66.00043859649124</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1544188.397129187</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>72.04358054226475</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>25.29959477862291</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>182.9713621416946</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>65.41922144351813</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1921685.820573288</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>70.70330820075066</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>167</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>27.4080808080808</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>183.0575757575758</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.100505050505051</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>67.32020202020202</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1364924.242424242</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>70.27929292929292</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>182.3861111111111</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.022222222222222</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>66.08611111111111</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1593819.444444444</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>73.26388888888889</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>22.98535401002506</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>183.0119439223058</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.013157894736842</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>61.81488878446115</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>995697.8383458648</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>70.15072838345864</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>22.72417675204053</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>179.979083309879</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.099299043062201</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>62.95826175063327</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1411628.570925978</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>72.03322628764424</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>167</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>24.41818181818182</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>181.9072727272727</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>67.47999999999999</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2451763.636363636</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>72.60909090909091</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>25.71515151515151</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>181.5777777777778</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>67.96848484848485</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3256979.797979798</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>71.9670707070707</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>24.24963768115942</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>181.0010869565218</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>62.5018115942029</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2158038.043478261</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>67.71992753623189</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>24.10215617715618</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>179.5005869130869</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>65.57434648684651</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2294799.034299034</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>71.5803071928072</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>167</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>25.08863636363637</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.481818181818182</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>71.58636363636363</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4704659.090909091</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>76.64772727272727</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26.81636363636363</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>183.5054545454545</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.130909090909091</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>71.67999999999999</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3297909.090909091</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>74.01636363636364</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>22.93650793650794</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>183.6582341269841</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.058035714285714</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>67.1889880952381</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2308774.801587301</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>75.2936507936508</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>24.64467787114846</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>183.4112324929972</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.107002801120448</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>64.26168067226891</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1267851.820728291</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>70.42638655462186</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>167</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>26.22000000000001</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>179.56</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2493500</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>181.1822222222223</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.064444444444444</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>67.1888888888889</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1839666.666666667</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>70.89333333333335</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>26.40372670807453</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>180.0136645962733</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.363975155279503</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>67.33540372670807</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3346997.929606625</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>71.22981366459626</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>25.79668655868145</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>180.4664052287582</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.073796533105996</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>66.03312020460359</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1435218.456947997</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>71.12160272804775</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>167</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>27.54080808080808</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>181.0583838383838</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.259393939393939</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>67.24242424242425</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2580970.707070707</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>69.31171717171716</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>181.4822222222222</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.204444444444444</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>67.04666666666667</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2133166.666666667</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>68.56888888888889</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>24.24339826839827</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>181.7162878787879</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.194318181818182</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>63.82202380952381</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1859379.87012987</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>68.54431818181817</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>28.31732040905954</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>179.8015672250455</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.190493757450279</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>66.54496455235585</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1245346.87245122</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>67.8298795407491</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>167</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>26.25757575757576</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>182.8484848484848</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>68.53030303030303</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2365151.515151516</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>71.68181818181817</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>65.67999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2039000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>73.42</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>24.87184560132215</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>180.9194555682685</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.006944444444444</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>64.20262840071193</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1107212.329964404</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>69.16638062547675</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>23.35241228070175</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>181.4065789473684</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>63.35486842105263</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1277069.152046784</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>71.19820175438596</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>167</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>27.23272727272727</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>181.4945454545455</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.192727272727273</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>68.55454545454546</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2028936.363636364</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>71.60727272727273</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>24.98686868686869</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>179.5739393939394</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>66.33656565656565</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1722348.484848485</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>71.9979797979798</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>25.52729315583536</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>178.0795901370581</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>65.21619122565414</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1096387.178394212</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>68.50703106214614</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>26.40285714285715</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>179.4809523809524</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>66.09301587301586</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1449616.26984127</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>69.95849206349207</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>25.17558922558922</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>182.3321548821549</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.191582491582492</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>66.94208754208753</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2060681.818181818</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>70.88249158249158</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>25.12727272727273</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>181.1287878787878</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>65.37272727272727</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1297598.484848485</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>70.18939393939394</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>23.80319211017741</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>182.152293417367</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.019607843137255</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>62.80070611577964</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1130583.129084967</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>69.09622432306256</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>25.33894478844169</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>177.8566821465429</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>64.80256707946337</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1459503.515221878</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>69.66224845201238</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.9375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>24.27111111111111</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>179.8355555555555</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>64.88444444444444</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1324855.555555556</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>69.89777777777778</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>26.64727272727272</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>177.6054545454545</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>69.10363636363635</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2108863.636363636</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>71.87272727272727</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>21.35765480895916</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>180.5926482213439</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>58.3937417654809</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>610425.1646903821</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>68.52461133069828</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>25.45601449275362</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>181.6361231884058</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>66.73724637681158</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1481006.884057971</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>69.84210144927536</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="n">
+        <v>26.43333333333333</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>70.63333333333334</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3900833.333333333</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>74.05000000000001</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>28.60303030303031</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>180.7015151515151</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.387878787878788</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>72.35757575757576</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>4027651.515151516</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>74.58939393939393</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>24.49826824004456</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>180.1154274575327</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.105054302422724</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>64.77993595098859</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1900719.028473963</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>70.15235136452242</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>25.08525167642815</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>179.6502504031916</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.055952380952381</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>67.4250233426704</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2096077.794754266</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>73.7279602750191</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>25.3810606060606</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>176.6742424242424</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>68.99747474747474</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2828598.484848485</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>72.10277777777777</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>179.5333333333333</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>68.85000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2990166.666666667</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>71.73333333333333</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>25.29416996047431</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>178.5049407114624</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>65.23908102766799</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1289512.104743083</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>69.50578063241107</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>26.38565217391304</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>180.1132125603865</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>65.94187747035573</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1450997.51866491</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>69.38378238910848</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC15"/>
+  <dimension ref="A1:AS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,42 +515,42 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_rat_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_wage_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -565,140 +565,90 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +657,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71000</v>
+        <v>54251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -763,166 +713,132 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>31</v>
+        <v>22.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>176.5</v>
+        <v>180.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
-        <v>127</v>
-      </c>
       <c r="U2" t="n">
-        <v>775000</v>
+        <v>111</v>
       </c>
       <c r="V2" t="n">
-        <v>130</v>
+        <v>23.6</v>
       </c>
       <c r="W2" t="n">
-        <v>27.33333333333333</v>
+        <v>181</v>
       </c>
       <c r="X2" t="n">
-        <v>180</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>6000</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>200</v>
+        <v>357</v>
       </c>
       <c r="AB2" t="n">
-        <v>3250000</v>
+        <v>24.47569444444444</v>
       </c>
       <c r="AC2" t="n">
-        <v>200</v>
+        <v>181.0034722222222</v>
       </c>
       <c r="AD2" t="n">
-        <v>27.95681818181818</v>
+        <v>67.65277777777779</v>
       </c>
       <c r="AE2" t="n">
-        <v>179.8477272727273</v>
+        <v>4833.333333333333</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.095454545454546</v>
+        <v>25.14545454545454</v>
       </c>
       <c r="AG2" t="n">
-        <v>67.44318181818181</v>
+        <v>182.8909090909091</v>
       </c>
       <c r="AH2" t="n">
-        <v>1518420.454545455</v>
+        <v>71.73181818181818</v>
       </c>
       <c r="AI2" t="n">
-        <v>69.23409090909091</v>
+        <v>11000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27.52954545454546</v>
+        <v>22.39038265954742</v>
       </c>
       <c r="AK2" t="n">
-        <v>183.1909090909091</v>
+        <v>179.6634846173405</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.140909090909091</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>67.88636363636364</v>
-      </c>
+        <v>61.65174294431732</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>3033977.272727272</v>
+        <v>23.48430735930736</v>
       </c>
       <c r="AO2" t="n">
-        <v>69.25681818181818</v>
+        <v>182.8602543290043</v>
       </c>
       <c r="AP2" t="n">
-        <v>25.56666666666667</v>
+        <v>68.50716991341992</v>
       </c>
       <c r="AQ2" t="n">
-        <v>179.4208333333333</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>65.79375</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1768723.958333333</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>70.55104166666666</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>26.74865472504791</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>183.031383606074</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>62.94452307238685</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>706806.1606221437</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>65.64766143299425</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>63fk89be</t>
+        <v>11380.95238095238</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23112</v>
+        <v>74867</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -949,157 +865,125 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>185</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>67</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1100000</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>69</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W3" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>137</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>179.7727272727273</v>
+      </c>
       <c r="AD3" t="n">
-        <v>23.61111111111111</v>
+        <v>69.52272727272727</v>
       </c>
       <c r="AE3" t="n">
-        <v>179.6866161616161</v>
+        <v>8409.090909090908</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.047727272727273</v>
+        <v>26.68888888888889</v>
       </c>
       <c r="AG3" t="n">
-        <v>66.11792929292929</v>
+        <v>180.2222222222222</v>
       </c>
       <c r="AH3" t="n">
-        <v>1408484.848484849</v>
+        <v>68.37777777777778</v>
       </c>
       <c r="AI3" t="n">
-        <v>72.30883838383838</v>
+        <v>4722.222222222223</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26.54545454545455</v>
+        <v>25.23826777087647</v>
       </c>
       <c r="AK3" t="n">
-        <v>180.4545454545455</v>
+        <v>182.2712790430182</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>65.98510466988728</v>
       </c>
       <c r="AM3" t="n">
-        <v>68.47727272727272</v>
+        <v>4649.413388543823</v>
       </c>
       <c r="AN3" t="n">
-        <v>2205681.818181818</v>
+        <v>26.08694099378882</v>
       </c>
       <c r="AO3" t="n">
-        <v>72.54545454545455</v>
+        <v>179.5517460317461</v>
       </c>
       <c r="AP3" t="n">
-        <v>23.48036283891547</v>
+        <v>67.26191338854383</v>
       </c>
       <c r="AQ3" t="n">
-        <v>177.669158692185</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.087968500797448</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>66.12554824561404</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1564454.246411483</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>72.23155901116428</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>25.05631165509682</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>183.6005663134819</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>64.84220862257946</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1704039.093898429</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>70.28822616002923</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
+        <v>3642.857142857143</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20000</v>
+        <v>23112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1124,165 +1008,125 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>187</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>183</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3250000</v>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>223</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>20</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>181.3333333333333</v>
+        <v>67.66666666666667</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>3666.666666666667</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="AB4" t="n">
-        <v>4520000</v>
+        <v>22.59343434343434</v>
       </c>
       <c r="AC4" t="n">
-        <v>218</v>
+        <v>179.4441919191919</v>
       </c>
       <c r="AD4" t="n">
-        <v>27.4080808080808</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>183.2575757575758</v>
-      </c>
+        <v>65.83510101010101</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>1.100505050505051</v>
+        <v>25.94545454545455</v>
       </c>
       <c r="AG4" t="n">
-        <v>67.29520202020201</v>
+        <v>183.0363636363636</v>
       </c>
       <c r="AH4" t="n">
-        <v>1373049.242424242</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>70.17929292929293</v>
-      </c>
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>23.19444444444445</v>
+        <v>23.10437077542341</v>
       </c>
       <c r="AK4" t="n">
-        <v>182.3715277777778</v>
+        <v>177.5253094858358</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.027777777777778</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>66.27430555555556</v>
-      </c>
+        <v>65.97128237259817</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>1610329.861111111</v>
+        <v>24.875</v>
       </c>
       <c r="AO4" t="n">
-        <v>73.27430555555556</v>
+        <v>179.4781055900621</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.75271512113617</v>
+        <v>64.04549689440994</v>
       </c>
       <c r="AQ4" t="n">
-        <v>182.5136800334169</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.027046783625731</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>62.5110693400167</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1037329.782790309</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>69.94413116123643</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>22.81698564593302</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>179.0915011961723</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.124123803827751</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>62.75665071770335</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1402771.00777512</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>72.23270933014354</v>
-      </c>
-      <c r="BB4" t="inlineStr">
+        <v>2750</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26000</v>
+        <v>20371</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1309,171 +1153,137 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>nezMCpx2</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q5" t="n">
-        <v>186.8</v>
+        <v>186</v>
       </c>
       <c r="R5" t="n">
+        <v>63</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>320</v>
-      </c>
       <c r="U5" t="n">
-        <v>4835000</v>
+        <v>63</v>
       </c>
       <c r="V5" t="n">
-        <v>337</v>
+        <v>25</v>
       </c>
       <c r="W5" t="n">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="X5" t="n">
-        <v>187.5</v>
+        <v>58</v>
       </c>
       <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
       <c r="AA5" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="AB5" t="n">
-        <v>525000</v>
+        <v>25.32080808080809</v>
       </c>
       <c r="AC5" t="n">
-        <v>130</v>
+        <v>181.5822222222222</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.15909090909091</v>
+        <v>67.64545454545456</v>
       </c>
       <c r="AE5" t="n">
-        <v>182.2704545454545</v>
+        <v>3777.575757575758</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>25.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>66.96363636363637</v>
+        <v>179.725</v>
       </c>
       <c r="AH5" t="n">
-        <v>2174931.818181818</v>
+        <v>69.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.44318181818183</v>
+        <v>4650</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25.58989898989899</v>
+        <v>25.01079386299974</v>
       </c>
       <c r="AK5" t="n">
-        <v>181.4222222222222</v>
+        <v>179.8680131143366</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>67.22570664629488</v>
       </c>
       <c r="AM5" t="n">
-        <v>67.55636363636364</v>
+        <v>3891.273554876496</v>
       </c>
       <c r="AN5" t="n">
-        <v>2894353.535353535</v>
+        <v>27.01086956521739</v>
       </c>
       <c r="AO5" t="n">
-        <v>71.75696969696969</v>
+        <v>178.8354037267081</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.27038043478261</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>180.7721920289855</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>62.95018115942029</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2430255.887681159</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>68.01449275362319</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>24.68965617715618</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>179.8726107226107</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>66.22077505827505</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2156760.343822843</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>71.44399766899767</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
+        <v>68.58178053830228</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">penso c 
+  usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21550</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1498,173 +1308,129 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="Q6" t="n">
-        <v>178.5</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>20666.66666666667</v>
       </c>
       <c r="T6" t="n">
-        <v>148</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>15000000</v>
+        <v>197</v>
       </c>
       <c r="V6" t="n">
-        <v>158</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>21</v>
+        <v>176.6666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>175</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
+        <v>64.66666666666667</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>56</v>
+        <v>194</v>
       </c>
       <c r="AB6" t="n">
-        <v>275000</v>
+        <v>22.33535353535353</v>
       </c>
       <c r="AC6" t="n">
-        <v>63</v>
+        <v>180.135101010101</v>
       </c>
       <c r="AD6" t="n">
-        <v>25.08863636363637</v>
+        <v>65.67424242424242</v>
       </c>
       <c r="AE6" t="n">
-        <v>183.75</v>
+        <v>2666.666666666667</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.481818181818182</v>
+        <v>28.125</v>
       </c>
       <c r="AG6" t="n">
-        <v>71.58636363636363</v>
+        <v>181.175</v>
       </c>
       <c r="AH6" t="n">
-        <v>4704659.090909091</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AI6" t="n">
-        <v>76.64772727272727</v>
+        <v>7150</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26.94545454545455</v>
+        <v>22.81666666666666</v>
       </c>
       <c r="AK6" t="n">
-        <v>183.3318181818182</v>
+        <v>180.3875</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.163636363636364</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>71.875</v>
-      </c>
+        <v>62.95833333333334</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>3367386.363636364</v>
+        <v>25.4143665158371</v>
       </c>
       <c r="AO6" t="n">
-        <v>74.34545454545454</v>
+        <v>178.6046945701357</v>
       </c>
       <c r="AP6" t="n">
-        <v>22.93650793650794</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>183.6582341269841</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.058035714285714</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>67.1889880952381</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2308774.801587301</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>75.2936507936508</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24.52251400560224</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>183.5807072829132</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.08375350140056</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>64.57710084033613</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1357981.442577031</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>70.58298319327731</v>
-      </c>
-      <c r="BB6" t="inlineStr">
+        <v>65.99688914027149</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>6LuGZiZI</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso t 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25500</v>
+        <v>20738</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1691,167 +1457,125 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>180</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>69</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1200000</v>
-      </c>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>69</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>24</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="X7" t="n">
-        <v>179</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="AB7" t="n">
-        <v>7500000</v>
+        <v>28.07222222222222</v>
       </c>
       <c r="AC7" t="n">
-        <v>78</v>
+        <v>181.775</v>
       </c>
       <c r="AD7" t="n">
-        <v>26.175</v>
+        <v>67.6888888888889</v>
       </c>
       <c r="AE7" t="n">
-        <v>179.525</v>
+        <v>5291.666666666666</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.05</v>
+        <v>27.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>69.8</v>
+        <v>181.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>2486250</v>
+        <v>68.24000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.69999999999999</v>
+        <v>4000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26.78</v>
+        <v>28.61507936507937</v>
       </c>
       <c r="AK7" t="n">
-        <v>180.8933333333334</v>
+        <v>179.828529657477</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.086666666666666</v>
+        <v>66.87990810359231</v>
       </c>
       <c r="AM7" t="n">
-        <v>67.43333333333332</v>
+        <v>3972.988025619605</v>
       </c>
       <c r="AN7" t="n">
-        <v>2221333.333333333</v>
+        <v>25.08768453768454</v>
       </c>
       <c r="AO7" t="n">
-        <v>70.76000000000001</v>
+        <v>177.444289044289</v>
       </c>
       <c r="AP7" t="n">
-        <v>26.50465838509317</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>180.082298136646</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.357142857142857</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>67.54968944099379</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3391030.020703933</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>71.31987577639751</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>26.01414687614176</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>180.1981512605042</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.076971136280599</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>66.49026306174645</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1536408.933138473</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>70.9692217756668</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>WSL0wFD4</t>
+        <v>65.42167832167831</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30991</v>
+        <v>20500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1878,171 +1602,131 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
           <t>2i4sdl32</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>182</v>
+        <v>177.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>65.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="T8" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>775000</v>
+        <v>131</v>
       </c>
       <c r="V8" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="X8" t="n">
-        <v>188</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
+        <v>64.5</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="AB8" t="n">
-        <v>275000</v>
+        <v>27.15909090909091</v>
       </c>
       <c r="AC8" t="n">
-        <v>63</v>
+        <v>181.5454545454546</v>
       </c>
       <c r="AD8" t="n">
-        <v>27.7760101010101</v>
+        <v>67.44545454545454</v>
       </c>
       <c r="AE8" t="n">
-        <v>180.6729797979798</v>
+        <v>3913.636363636364</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.299242424242424</v>
+        <v>29.09454545454545</v>
       </c>
       <c r="AG8" t="n">
-        <v>67.5030303030303</v>
+        <v>181.2636363636364</v>
       </c>
       <c r="AH8" t="n">
-        <v>2804963.383838383</v>
+        <v>73.04727272727273</v>
       </c>
       <c r="AI8" t="n">
-        <v>69.36464646464646</v>
+        <v>16554.54545454545</v>
       </c>
       <c r="AJ8" t="n">
-        <v>28.125</v>
+        <v>23.53013738390093</v>
       </c>
       <c r="AK8" t="n">
-        <v>181.6777777777777</v>
+        <v>178.5794794891641</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.180555555555555</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>67.03333333333333</v>
-      </c>
+        <v>65.96062306501548</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>2088958.333333333</v>
+        <v>25.20634669678148</v>
       </c>
       <c r="AO8" t="n">
-        <v>68.58611111111111</v>
+        <v>179.9483079239601</v>
       </c>
       <c r="AP8" t="n">
-        <v>24.09970238095238</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>181.7135416666667</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.140625</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>63.77752976190476</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1610133.928571429</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>68.578125</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>28.51621572871573</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>179.7410894660895</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.216378066378067</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>66.87685786435786</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1316357.503607504</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>67.97213203463204</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
+        <v>67.42166760775456</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>61500</v>
+        <v>30000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2069,167 +1753,133 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
       <c r="P9" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>66</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>132</v>
+      </c>
+      <c r="V9" t="n">
         <v>27</v>
       </c>
-      <c r="Q9" t="n">
-        <v>183</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>64</v>
-      </c>
-      <c r="U9" t="n">
-        <v>575000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>64</v>
-      </c>
       <c r="W9" t="n">
-        <v>25.5</v>
+        <v>181.4</v>
       </c>
       <c r="X9" t="n">
-        <v>181</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>130</v>
+        <v>330</v>
       </c>
       <c r="AB9" t="n">
-        <v>17600000</v>
+        <v>28.09772727272728</v>
       </c>
       <c r="AC9" t="n">
-        <v>141</v>
+        <v>183.9181818181818</v>
       </c>
       <c r="AD9" t="n">
-        <v>26.07272727272727</v>
+        <v>69.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>182.8727272727272</v>
+        <v>4859.090909090909</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.090909090909091</v>
+        <v>24.525</v>
       </c>
       <c r="AG9" t="n">
-        <v>68.34545454545454</v>
+        <v>181.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>2360000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>71.74545454545455</v>
-      </c>
+        <v>69.64999999999999</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
-        <v>22.37272727272727</v>
+        <v>25.96090102707749</v>
       </c>
       <c r="AK9" t="n">
-        <v>180.3036363636364</v>
+        <v>184.2954014939309</v>
       </c>
       <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>65.31272727272727</v>
-      </c>
+        <v>61.69549486461251</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>1893236.363636364</v>
+        <v>24.48913043478261</v>
       </c>
       <c r="AO9" t="n">
-        <v>73.09272727272726</v>
+        <v>181.1471920289855</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.83152173913044</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>180.3541925465838</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.017857142857143</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>64.11614906832298</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1141037.784679089</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>68.96055900621118</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>22.92083333333333</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>180.615</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>63.03416666666667</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1290497.222222222</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>71.62416666666667</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
+        <v>62.05434782608696</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>21650</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2256,157 +1906,139 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>23.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="R10" t="n">
+        <v>64</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>182</v>
-      </c>
       <c r="U10" t="n">
-        <v>2155000</v>
+        <v>64</v>
       </c>
       <c r="V10" t="n">
-        <v>203</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+        <v>32.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>187</v>
+      </c>
+      <c r="X10" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>127</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>27.96363636363636</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>180.2727272727273</v>
+      </c>
       <c r="AD10" t="n">
-        <v>27.2</v>
+        <v>66.89090909090909</v>
       </c>
       <c r="AE10" t="n">
-        <v>181.3745454545455</v>
+        <v>3836.363636363636</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.196363636363637</v>
+        <v>26.175</v>
       </c>
       <c r="AG10" t="n">
-        <v>68.54363636363637</v>
+        <v>181.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>2017581.818181818</v>
+        <v>68.05</v>
       </c>
       <c r="AI10" t="n">
-        <v>71.56</v>
+        <v>4800</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24.98358585858586</v>
+        <v>26.0630303030303</v>
       </c>
       <c r="AK10" t="n">
-        <v>179.9174242424242</v>
+        <v>178.8027272727273</v>
       </c>
       <c r="AL10" t="n">
-        <v>1</v>
+        <v>64.77909090909091</v>
       </c>
       <c r="AM10" t="n">
-        <v>65.99570707070707</v>
+        <v>2818.181818181818</v>
       </c>
       <c r="AN10" t="n">
-        <v>1596685.606060606</v>
+        <v>24.63422191619123</v>
       </c>
       <c r="AO10" t="n">
-        <v>71.72247474747475</v>
+        <v>179.0017757851248</v>
       </c>
       <c r="AP10" t="n">
-        <v>25.50278335191378</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>177.7501783723523</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>65.82207357859531</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1225691.099962839</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>69.24624674842066</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>26.50357142857143</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>179.7011904761905</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>66.34126984126983</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1450270.337301587</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>69.84811507936509</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
+        <v>63.49161679281816</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22423</v>
+        <v>18061</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2433,152 +2065,118 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q11" t="n">
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>32</v>
+      </c>
+      <c r="W11" t="n">
+        <v>190</v>
+      </c>
+      <c r="X11" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>69</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.33333333333334</v>
+      </c>
+      <c r="AC11" t="n">
         <v>179.6666666666667</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>201</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3975000</v>
-      </c>
-      <c r="V11" t="n">
-        <v>212</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>25.44909090909091</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>183.3581818181818</v>
-      </c>
+        <v>64.44444444444444</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>1.185454545454546</v>
+        <v>27.50555555555556</v>
       </c>
       <c r="AG11" t="n">
-        <v>68.04363636363637</v>
+        <v>180.0388888888889</v>
       </c>
       <c r="AH11" t="n">
-        <v>2316454.545454545</v>
+        <v>67.44166666666668</v>
       </c>
       <c r="AI11" t="n">
-        <v>71.39636363636365</v>
+        <v>4900</v>
       </c>
       <c r="AJ11" t="n">
-        <v>25.34090909090909</v>
+        <v>21.50378787878788</v>
       </c>
       <c r="AK11" t="n">
-        <v>181.6681818181818</v>
+        <v>179.3465909090909</v>
       </c>
       <c r="AL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>66.05909090909091</v>
-      </c>
+        <v>59.42424242424243</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>1416022.727272727</v>
+        <v>23.83690476190476</v>
       </c>
       <c r="AO11" t="n">
-        <v>70.75909090909092</v>
+        <v>182.9376217532468</v>
       </c>
       <c r="AP11" t="n">
-        <v>23.85980576441103</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>181.4081390977444</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>63.58623433583959</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1294702.850877193</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>69.36067042606517</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>25.24448529411765</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>178.0195433436533</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>64.30756578947368</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1384851.248065015</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>69.04523026315789</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>UFWZoX9L</t>
+        <v>62.71873647186148</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45549.9375</v>
+        <v>45556.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">penso t 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18061</v>
+        <v>20213</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2610,7 +2208,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2618,143 +2216,89 @@
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>184</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>124</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1675000</v>
-      </c>
-      <c r="V12" t="n">
-        <v>148</v>
-      </c>
-      <c r="W12" t="n">
-        <v>26</v>
-      </c>
-      <c r="X12" t="n">
-        <v>178</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>65</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="n">
-        <v>775000</v>
+        <v>24.41666666666667</v>
       </c>
       <c r="AC12" t="n">
-        <v>65</v>
+        <v>181.0555555555555</v>
       </c>
       <c r="AD12" t="n">
-        <v>24.18518518518519</v>
+        <v>65.27777777777777</v>
       </c>
       <c r="AE12" t="n">
-        <v>179.9259259259259</v>
+        <v>5111.111111111111</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>26.30909090909091</v>
       </c>
       <c r="AG12" t="n">
-        <v>64.74074074074075</v>
+        <v>177.9318181818182</v>
       </c>
       <c r="AH12" t="n">
-        <v>1354259.259259259</v>
+        <v>69.72954545454544</v>
       </c>
       <c r="AI12" t="n">
-        <v>69.96296296296295</v>
+        <v>4268.181818181818</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26.51212121212121</v>
+        <v>26.3078431372549</v>
       </c>
       <c r="AK12" t="n">
-        <v>177.7090909090909</v>
+        <v>179.6095811051694</v>
       </c>
       <c r="AL12" t="n">
-        <v>1</v>
+        <v>65.90352049910874</v>
       </c>
       <c r="AM12" t="n">
-        <v>69.47272727272727</v>
+        <v>4236.244800950683</v>
       </c>
       <c r="AN12" t="n">
-        <v>2333106.060606061</v>
+        <v>25.55339912280702</v>
       </c>
       <c r="AO12" t="n">
-        <v>72.35454545454546</v>
+        <v>181.415076754386</v>
       </c>
       <c r="AP12" t="n">
-        <v>21.80164690382081</v>
+        <v>67.03114035087719</v>
       </c>
       <c r="AQ12" t="n">
-        <v>180.2544137022398</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>59.24512516469039</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>696930.8300395258</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>68.4965744400527</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>25.48176328502415</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>181.9442632850241</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>66.89468599033817</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1532591.183574879</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>69.83683574879228</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
+        <v>3129.934210526316</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
@@ -2774,7 +2318,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2800,164 +2344,134 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="R13" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>137</v>
+      </c>
+      <c r="V13" t="n">
+        <v>22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>180</v>
+      </c>
+      <c r="X13" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>76</v>
-      </c>
-      <c r="W13" t="n">
-        <v>24</v>
-      </c>
-      <c r="X13" t="n">
-        <v>186</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2</v>
-      </c>
       <c r="AA13" t="n">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="AB13" t="n">
-        <v>2000000</v>
+        <v>26.34545454545454</v>
       </c>
       <c r="AC13" t="n">
-        <v>139</v>
+        <v>178.8227272727273</v>
       </c>
       <c r="AD13" t="n">
-        <v>26.4</v>
+        <v>70.77272727272727</v>
       </c>
       <c r="AE13" t="n">
-        <v>177.775</v>
+        <v>7681.818181818182</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.075</v>
+        <v>25.38636363636364</v>
       </c>
       <c r="AG13" t="n">
-        <v>70.52500000000001</v>
+        <v>177.9545454545455</v>
       </c>
       <c r="AH13" t="n">
-        <v>3875625</v>
+        <v>68.06818181818183</v>
       </c>
       <c r="AI13" t="n">
-        <v>74.075</v>
+        <v>4227.272727272728</v>
       </c>
       <c r="AJ13" t="n">
-        <v>28.88363636363637</v>
+        <v>25.17845750740488</v>
       </c>
       <c r="AK13" t="n">
-        <v>181.2309090909091</v>
+        <v>179.5991968557758</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.403636363636364</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>72.66363636363636</v>
-      </c>
+        <v>66.44036226930965</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="n">
-        <v>3939772.727272728</v>
+        <v>25.39449006875478</v>
       </c>
       <c r="AO13" t="n">
-        <v>74.46363636363637</v>
+        <v>179.9436401833461</v>
       </c>
       <c r="AP13" t="n">
-        <v>25.02371814954052</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>179.9099832915622</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.144423558897243</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>65.06464076858813</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1994499.595342523</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>69.89957967836257</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>24.82230201171378</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>179.571209574739</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.057142857142857</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>66.61002801120449</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1853929.717341482</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>73.55173414820474</v>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>WSL0wFD4</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
+        <v>65.85572001527885</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
+          <t xml:space="preserve">montero r 
+  cos </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54405</v>
+        <v>18000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2982,325 +2496,100 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>18</v>
+        <v>26.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>191</v>
+        <v>183.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>71.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>6250</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>110000</v>
+        <v>286</v>
       </c>
       <c r="V14" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="W14" t="n">
-        <v>27</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="X14" t="n">
-        <v>180.5</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>3333.333333333333</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="AB14" t="n">
-        <v>2900000</v>
+        <v>25.39242424242424</v>
       </c>
       <c r="AC14" t="n">
-        <v>140</v>
+        <v>179.1974747474748</v>
       </c>
       <c r="AD14" t="n">
-        <v>25.18156565656566</v>
+        <v>67.74545454545455</v>
       </c>
       <c r="AE14" t="n">
-        <v>177.6338383838384</v>
+        <v>5200</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AG14" t="n">
-        <v>68.25</v>
+        <v>184.4545454545455</v>
       </c>
       <c r="AH14" t="n">
-        <v>2416414.141414142</v>
+        <v>69.13636363636364</v>
       </c>
       <c r="AI14" t="n">
-        <v>71.63560606060607</v>
+        <v>7090.909090909091</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26.125</v>
+        <v>26.35869565217391</v>
       </c>
       <c r="AK14" t="n">
-        <v>179.45</v>
+        <v>180.1304347826087</v>
       </c>
       <c r="AL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>68.72500000000001</v>
-      </c>
+        <v>66.16304347826087</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="n">
-        <v>3029250</v>
+        <v>24.22842492260062</v>
       </c>
       <c r="AO14" t="n">
-        <v>71.8</v>
+        <v>181.7563660990712</v>
       </c>
       <c r="AP14" t="n">
-        <v>25.4337803500847</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>179.089356295878</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>65.51505505364202</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1358870.870976849</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>69.74117024280068</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>25.95347826086957</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>179.815652173913</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>65.4753162055336</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1361912.944664031</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>69.44025691699605</v>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
+        <v>64.80268962848298</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
         <is>
           <t>UFWZoX9L</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45550.84375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>167</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>33.66666666666666</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>177</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>222</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8650000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>222</v>
-      </c>
-      <c r="W15" t="n">
-        <v>26</v>
-      </c>
-      <c r="X15" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>199</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>208</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>26.58657407407408</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>179.5768518518519</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.186111111111111</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>69.17962962962963</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2542986.111111111</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>72.56157407407407</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>27.69090909090909</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>180.7818181818182</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.054545454545455</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>66.52727272727273</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1253090.909090909</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>69.05454545454545</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>24.60966301979728</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>177.9542708629345</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.166730605285592</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>66.78617860187553</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2797458.836553945</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>73.18940513403429</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>26.21969696969698</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>179.3093939393939</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.078333333333334</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>64.11409090909092</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1010582.575757576</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>67.83500000000001</v>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
         </is>
       </c>
     </row>
